--- a/Result/profitability/8068.xlsx
+++ b/Result/profitability/8068.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.25</v>
       </c>
       <c r="M2" t="n">
-        <v>0.215</v>
+        <v>0.13625</v>
       </c>
       <c r="N2" t="n">
-        <v>6.648750000000001</v>
+        <v>7.483750000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.87</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03499999999999998</v>
+        <v>-0.01000000000000002</v>
       </c>
       <c r="N3" t="n">
-        <v>6.487500000000001</v>
+        <v>7.84625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.55</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.07125000000000004</v>
+        <v>-0.08375000000000002</v>
       </c>
       <c r="N4" t="n">
-        <v>7.172499999999999</v>
+        <v>8.022500000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.44</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.13125</v>
+        <v>-0.2925</v>
       </c>
       <c r="N5" t="n">
-        <v>6.19125</v>
+        <v>7.3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.27</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.31875</v>
+        <v>-0.32375</v>
       </c>
       <c r="N6" t="n">
-        <v>6.68375</v>
+        <v>7.4725</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.6</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.39125</v>
+        <v>-0.395</v>
       </c>
       <c r="N7" t="n">
-        <v>6.95625</v>
+        <v>8.115</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.44</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4425000000000001</v>
+        <v>-0.4350000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>7.43125</v>
+        <v>7.1825</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>-0.3</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4650000000000001</v>
+        <v>-0.465</v>
       </c>
       <c r="N9" t="n">
         <v>6.14875</v>
@@ -1645,7 +1645,7 @@
         <v>-0.19</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4575000000000001</v>
+        <v>-0.4575</v>
       </c>
       <c r="N10" t="n">
         <v>5.69625</v>
@@ -9842,6 +9842,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8068</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>358</v>
+      </c>
+      <c r="D75" t="n">
+        <v>313</v>
+      </c>
+      <c r="E75" t="n">
+        <v>46</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-2.70%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.23875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>6.858750000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.989999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1353741496598638</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.048780487804878</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>8.870000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>2.309895833333333</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
